--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Documents\GitHub\wu_dslab_infrared-city\timesheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7F8508-7E2F-4DE7-9D03-942669E395EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527A64EE-2652-4509-BBD5-661975FC3197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39160" yWindow="760" windowWidth="28800" windowHeight="15910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27900" yWindow="11880" windowWidth="15024" windowHeight="11856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Date</t>
   </si>
@@ -47,10 +47,16 @@
     <t>Hours</t>
   </si>
   <si>
-    <t>Partizipation Lecture</t>
-  </si>
-  <si>
     <t>Sum Hours</t>
+  </si>
+  <si>
+    <t>partizipation of lecture</t>
+  </si>
+  <si>
+    <t>researched use of Vienna Baumkataster datasets, defined data coach questions, wrote meeting protocol</t>
+  </si>
+  <si>
+    <t>finalized meeting protocol, pushed protocol and latex template on github</t>
   </si>
 </sst>
 </file>
@@ -91,7 +97,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -369,15 +375,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.26953125" customWidth="1"/>
-    <col min="2" max="2" width="59.26953125" customWidth="1"/>
-    <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.21875" customWidth="1"/>
+    <col min="2" max="2" width="87" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -388,22 +394,44 @@
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46090</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>4</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527A64EE-2652-4509-BBD5-661975FC3197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA57D73-55EB-4EB9-8A7F-522F8FCF1099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27900" yWindow="11880" windowWidth="15024" windowHeight="11856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7080" yWindow="10236" windowWidth="15024" windowHeight="11856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Date</t>
   </si>
@@ -56,7 +56,10 @@
     <t>researched use of Vienna Baumkataster datasets, defined data coach questions, wrote meeting protocol</t>
   </si>
   <si>
-    <t>finalized meeting protocol, pushed protocol and latex template on github</t>
+    <t>finalized and pushed meeting protocol on github</t>
+  </si>
+  <si>
+    <t>pushed latex project proposal changes on github</t>
   </si>
 </sst>
 </file>
@@ -375,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -431,7 +434,18 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA57D73-55EB-4EB9-8A7F-522F8FCF1099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40644C24-859A-4DCF-92DD-DFBC43E66008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7080" yWindow="10236" windowWidth="15024" windowHeight="11856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6996" yWindow="9672" windowWidth="20136" windowHeight="14976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Date</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>pushed latex project proposal changes on github</t>
+  </si>
+  <si>
+    <t>finalized data coach questions and pushed on github for meeting</t>
   </si>
 </sst>
 </file>
@@ -378,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -412,7 +415,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -446,6 +449,17 @@
       </c>
       <c r="C5">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -1,81 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40644C24-859A-4DCF-92DD-DFBC43E66008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="6996" yWindow="9672" windowWidth="20136" windowHeight="14976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Descriptions</t>
-  </si>
-  <si>
-    <t>Hours</t>
-  </si>
-  <si>
-    <t>Sum Hours</t>
-  </si>
-  <si>
-    <t>partizipation of lecture</t>
-  </si>
-  <si>
-    <t>researched use of Vienna Baumkataster datasets, defined data coach questions, wrote meeting protocol</t>
-  </si>
-  <si>
-    <t>finalized and pushed meeting protocol on github</t>
-  </si>
-  <si>
-    <t>pushed latex project proposal changes on github</t>
-  </si>
-  <si>
-    <t>finalized data coach questions and pushed on github for meeting</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descriptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum Hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">partizipation of lecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">researched use of Vienna Baumkataster datasets, defined data coach questions, wrote meeting protocol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">finalized and pushed meeting protocol on github</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pushed latex project proposal changes on github</t>
+  </si>
+  <si>
+    <t xml:space="preserve">finalized data coach questions and pushed on github for meeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wrote third meeting protocol, finalized it afterwards and pushed it on github</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -87,7 +93,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -95,185 +101,144 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="44546a"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="e7e6e6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="5b9bd5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="ed7d31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="a5a5a5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="ffc000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4472c4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="70ad47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0563c1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="954f72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -281,33 +246,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -320,13 +276,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -336,15 +286,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -352,7 +300,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -360,109 +307,122 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="13.21875" customWidth="1"/>
-    <col min="2" max="2" width="87" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9.88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
         <v>46090</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="H2">
-        <f>SUM(C:C)</f>
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="H2" s="0" t="n">
+        <f aca="false">SUM(C:C)</f>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
         <v>46090</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
         <v>46091</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
         <v>46092</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
         <v>46093</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0" t="n">
         <v>1.5</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -1,17 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA5F1E1-B2C6-4E90-8D77-FCF98575A012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="21456" yWindow="9576" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -20,68 +36,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descriptions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum Hours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">partizipation of lecture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">researched use of Vienna Baumkataster datasets, defined data coach questions, wrote meeting protocol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">finalized and pushed meeting protocol on github</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pushed latex project proposal changes on github</t>
-  </si>
-  <si>
-    <t xml:space="preserve">finalized data coach questions and pushed on github for meeting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wrote third meeting protocol, finalized it afterwards and pushed it on github</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Descriptions</t>
+  </si>
+  <si>
+    <t>Hours</t>
+  </si>
+  <si>
+    <t>Sum Hours</t>
+  </si>
+  <si>
+    <t>researched use of Vienna Baumkataster datasets, defined data coach questions, wrote meeting protocol</t>
+  </si>
+  <si>
+    <t>finalized and pushed meeting protocol on github</t>
+  </si>
+  <si>
+    <t>pushed latex project proposal changes on github</t>
+  </si>
+  <si>
+    <t>finalized data coach questions and pushed on github for meeting</t>
+  </si>
+  <si>
+    <t>wrote third meeting protocol, finalized it afterwards and pushed it on github</t>
+  </si>
+  <si>
+    <t>made beam for the proposal and read through first chapter</t>
+  </si>
+  <si>
+    <t>meeting + writing protocol of proposal meeting</t>
+  </si>
+  <si>
+    <t>participation of lecture</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -93,7 +99,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -101,101 +107,78 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -227,7 +210,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -251,7 +234,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -311,118 +294,134 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9.88"/>
+    <col min="1" max="1" width="13.21875" customWidth="1"/>
+    <col min="2" max="2" width="87" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
         <v>46090</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
         <v>4</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="H2">
+        <f>SUM(C:C)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="0" t="n">
-        <f aca="false">SUM(C:C)</f>
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>46090</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>46091</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA5F1E1-B2C6-4E90-8D77-FCF98575A012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B857AE78-209C-4C34-867B-AB9AED2F4C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21456" yWindow="9576" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15204" yWindow="11088" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>participation of lecture</t>
+  </si>
+  <si>
+    <t>meeting, late due to work, but caught up</t>
+  </si>
+  <si>
+    <t>making juypter notebook file + starting writing scraper code</t>
   </si>
 </sst>
 </file>
@@ -306,7 +312,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -340,7 +346,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -418,6 +424,28 @@
       </c>
       <c r="C9">
         <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>46103</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B857AE78-209C-4C34-867B-AB9AED2F4C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAD18D1-6E72-4192-B688-F81480D20E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15204" yWindow="11088" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Date</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>making juypter notebook file + starting writing scraper code</t>
+  </si>
+  <si>
+    <t>finalized and pushed new meeting protocol on github</t>
   </si>
 </sst>
 </file>
@@ -312,7 +315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -346,7 +349,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>16</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -446,6 +449,17 @@
       </c>
       <c r="C11">
         <v>2.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAD18D1-6E72-4192-B688-F81480D20E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1212C8-5500-43B5-9CC8-80CD8F053F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15204" yWindow="11088" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13128" yWindow="11592" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>finalized and pushed new meeting protocol on github</t>
+  </si>
+  <si>
+    <t>continued wiht scraper code + foudn new datasets</t>
   </si>
 </sst>
 </file>
@@ -315,7 +318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -349,7 +352,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>16.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -460,6 +463,17 @@
       </c>
       <c r="C12">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1212C8-5500-43B5-9CC8-80CD8F053F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D735637C-383A-4786-9E77-F576FC25E72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13128" yWindow="11592" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15204" yWindow="11088" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Date</t>
   </si>
@@ -83,7 +83,13 @@
     <t>finalized and pushed new meeting protocol on github</t>
   </si>
   <si>
-    <t>continued wiht scraper code + foudn new datasets</t>
+    <t>continued with scraper code + found new datasets</t>
+  </si>
+  <si>
+    <t>continued writing scraper code for 3 new datasets + overworked juypter notebook text - sential, osm missing still</t>
+  </si>
+  <si>
+    <t>adding new beam chart to latex + proof reading</t>
   </si>
 </sst>
 </file>
@@ -318,11 +324,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
-    <col min="2" max="2" width="87" customWidth="1"/>
+    <col min="2" max="2" width="93.21875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -352,7 +358,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>18</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -474,6 +480,28 @@
       </c>
       <c r="C13">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>46109</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D735637C-383A-4786-9E77-F576FC25E72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C44C2D-86FA-41FA-B5AD-96EA938FD72C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15204" yWindow="11088" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Date</t>
   </si>
@@ -86,10 +86,16 @@
     <t>continued with scraper code + found new datasets</t>
   </si>
   <si>
-    <t>continued writing scraper code for 3 new datasets + overworked juypter notebook text - sential, osm missing still</t>
-  </si>
-  <si>
     <t>adding new beam chart to latex + proof reading</t>
+  </si>
+  <si>
+    <t>starting to clean the data (baumkataster of vienna, barcelona, paris and hamburg) e.g. datatypes, dup. etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">continued writing scraper code for 3 new datasets + overworked juypter notebook text </t>
+  </si>
+  <si>
+    <t>started handling missings the missings in the  vienna, barcelona, paris and hamburg datasets</t>
   </si>
 </sst>
 </file>
@@ -324,11 +330,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
-    <col min="2" max="2" width="93.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="96.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -358,7 +364,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>19.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -487,7 +493,7 @@
         <v>46107</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -498,10 +504,32 @@
         <v>46109</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>46110</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C44C2D-86FA-41FA-B5AD-96EA938FD72C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8453550B-40A9-4237-A272-06DB7F10AF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15204" yWindow="11088" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>started handling missings the missings in the  vienna, barcelona, paris and hamburg datasets</t>
+  </si>
+  <si>
+    <t>done cleaning baumkataster of vienna, barcelona, paris and hamburg</t>
+  </si>
+  <si>
+    <t>starting scraping sentinel/osm</t>
   </si>
 </sst>
 </file>
@@ -330,7 +336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -364,7 +370,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -529,7 +535,29 @@
         <v>19</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8453550B-40A9-4237-A272-06DB7F10AF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C1D586-0C58-4F6B-8E70-80E5310FE5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15204" yWindow="11088" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
     <t>done cleaning baumkataster of vienna, barcelona, paris and hamburg</t>
   </si>
   <si>
-    <t>starting scraping sentinel/osm</t>
+    <t>starting writing scraper for sentinel/osm</t>
   </si>
 </sst>
 </file>
@@ -370,7 +370,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>32</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -524,18 +524,18 @@
         <v>17</v>
       </c>
       <c r="C16">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>46111</v>
+        <v>46110</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
       </c>
       <c r="C17">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -546,7 +546,7 @@
         <v>20</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -557,7 +557,7 @@
         <v>21</v>
       </c>
       <c r="C19">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C1D586-0C58-4F6B-8E70-80E5310FE5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B37F8D9-21C8-4EF9-B8BC-CEE5AFD8ADBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15204" yWindow="11088" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7668" yWindow="7968" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Date</t>
   </si>
@@ -101,7 +101,10 @@
     <t>done cleaning baumkataster of vienna, barcelona, paris and hamburg</t>
   </si>
   <si>
-    <t>starting writing scraper for sentinel/osm</t>
+    <t>starting writing scraper for sentinel/osm -&gt; explored the  option of automating copernicus sentinel 2 API</t>
+  </si>
+  <si>
+    <t>exploring option google earth for sentinel</t>
   </si>
 </sst>
 </file>
@@ -336,7 +339,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -560,6 +563,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B37F8D9-21C8-4EF9-B8BC-CEE5AFD8ADBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5435397C-92E0-4586-A8F1-F48D6F07ECE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7668" yWindow="7968" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15204" yWindow="11088" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Date</t>
   </si>
@@ -71,12 +71,6 @@
     <t>meeting + writing protocol of proposal meeting</t>
   </si>
   <si>
-    <t>participation of lecture</t>
-  </si>
-  <si>
-    <t>meeting, late due to work, but caught up</t>
-  </si>
-  <si>
     <t>making juypter notebook file + starting writing scraper code</t>
   </si>
   <si>
@@ -101,10 +95,19 @@
     <t>done cleaning baumkataster of vienna, barcelona, paris and hamburg</t>
   </si>
   <si>
-    <t>starting writing scraper for sentinel/osm -&gt; explored the  option of automating copernicus sentinel 2 API</t>
-  </si>
-  <si>
-    <t>exploring option google earth for sentinel</t>
+    <t xml:space="preserve">meeting + writing protocol </t>
+  </si>
+  <si>
+    <t>participation of lecture + writing notes for project</t>
+  </si>
+  <si>
+    <t>starting writing scraper for sentinel/osm -&gt; explored the option of automating copernicus sentinel 2 API</t>
+  </si>
+  <si>
+    <t>exploring option google earth for sentinel -&gt; works better</t>
+  </si>
+  <si>
+    <t>scraping sentinel data, scraping osm + cleaning/saving</t>
   </si>
 </sst>
 </file>
@@ -339,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -366,14 +369,14 @@
         <v>46090</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>34.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -417,7 +420,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -439,7 +442,7 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -458,7 +461,7 @@
         <v>46100</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>0.5</v>
@@ -469,10 +472,10 @@
         <v>46103</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -480,7 +483,7 @@
         <v>46104</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>0.5</v>
@@ -491,10 +494,10 @@
         <v>46106</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -502,7 +505,7 @@
         <v>46107</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -513,7 +516,7 @@
         <v>46109</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C15">
         <v>0.5</v>
@@ -524,7 +527,7 @@
         <v>46110</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -535,7 +538,7 @@
         <v>46110</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -546,7 +549,7 @@
         <v>46111</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -570,6 +573,23 @@
       <c r="B20" t="s">
         <v>22</v>
       </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5435397C-92E0-4586-A8F1-F48D6F07ECE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C097C6BA-E098-4A6D-BA7A-60BA7A04B398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15204" yWindow="11088" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Date</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>scraping sentinel data, scraping osm + cleaning/saving</t>
+  </si>
+  <si>
+    <t>finalized notebooks (added descriptions, etc.)</t>
   </si>
 </sst>
 </file>
@@ -376,7 +379,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>45.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -589,7 +592,15 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
+      <c r="A22" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22">
+        <v>0.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C097C6BA-E098-4A6D-BA7A-60BA7A04B398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9352A68-4CB8-4B51-8857-B782EA597F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15204" yWindow="11088" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Date</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>finalized notebooks (added descriptions, etc.)</t>
+  </si>
+  <si>
+    <t>fixing typos in notebooks</t>
   </si>
 </sst>
 </file>
@@ -345,7 +348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -379,7 +382,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>46</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -599,6 +602,17 @@
         <v>24</v>
       </c>
       <c r="C22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23">
         <v>0.5</v>
       </c>
     </row>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\wu_dslab_infrared-city\timesheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vani1\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9352A68-4CB8-4B51-8857-B782EA597F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4857272-7B1D-4C2E-9DEB-9144F0E9A690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15204" yWindow="11088" windowWidth="19008" windowHeight="11856" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Date</t>
   </si>
@@ -101,9 +101,6 @@
     <t>participation of lecture + writing notes for project</t>
   </si>
   <si>
-    <t>starting writing scraper for sentinel/osm -&gt; explored the option of automating copernicus sentinel 2 API</t>
-  </si>
-  <si>
     <t>exploring option google earth for sentinel -&gt; works better</t>
   </si>
   <si>
@@ -114,6 +111,12 @@
   </si>
   <si>
     <t>fixing typos in notebooks</t>
+  </si>
+  <si>
+    <t>starting writing scraper for sentinel/osm -&gt; explored the option of automating copernicus sentinel 2 API -&gt; didnt work so well</t>
+  </si>
+  <si>
+    <t>wrote two meeting protocols and discussed EDA outcome with sara (no rescraping necessary)</t>
   </si>
 </sst>
 </file>
@@ -348,15 +351,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.21875" customWidth="1"/>
-    <col min="2" max="2" width="96.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" customWidth="1"/>
+    <col min="2" max="2" width="105.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -370,7 +373,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>46090</v>
       </c>
@@ -382,10 +385,10 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>46090</v>
       </c>
@@ -396,7 +399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>46091</v>
       </c>
@@ -407,7 +410,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>46092</v>
       </c>
@@ -418,7 +421,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>46093</v>
       </c>
@@ -429,7 +432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46094</v>
       </c>
@@ -440,7 +443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>46095</v>
       </c>
@@ -451,7 +454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>46096</v>
       </c>
@@ -462,7 +465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>46100</v>
       </c>
@@ -473,7 +476,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>46103</v>
       </c>
@@ -484,7 +487,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>46104</v>
       </c>
@@ -495,7 +498,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>46106</v>
       </c>
@@ -506,7 +509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>46107</v>
       </c>
@@ -517,7 +520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>46109</v>
       </c>
@@ -528,7 +531,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>46110</v>
       </c>
@@ -539,7 +542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>46110</v>
       </c>
@@ -550,7 +553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>46111</v>
       </c>
@@ -561,58 +564,69 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>46111</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>46112</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>46112</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>46112</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22">
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>46113</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24">
         <v>0.5</v>
       </c>
     </row>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vani1\wu_dslab_infrared-city\timesheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vani1\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4857272-7B1D-4C2E-9DEB-9144F0E9A690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E44A20C-6020-4C2A-8C94-FEE4791FC16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Date</t>
   </si>
@@ -110,13 +110,22 @@
     <t>finalized notebooks (added descriptions, etc.)</t>
   </si>
   <si>
-    <t>fixing typos in notebooks</t>
-  </si>
-  <si>
     <t>starting writing scraper for sentinel/osm -&gt; explored the option of automating copernicus sentinel 2 API -&gt; didnt work so well</t>
   </si>
   <si>
     <t>wrote two meeting protocols and discussed EDA outcome with sara (no rescraping necessary)</t>
+  </si>
+  <si>
+    <t>scraped osm data and satellite data for Innsbruck and Linz</t>
+  </si>
+  <si>
+    <t>fixing typos in notebooks and finialzed my chapter for intermediate report</t>
+  </si>
+  <si>
+    <t>wrote sparring group protocol for my group: suggestions, feedback etc.</t>
+  </si>
+  <si>
+    <t>scraped more baumkataster datasets for Innsbruck and Linz</t>
   </si>
 </sst>
 </file>
@@ -351,7 +360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.1796875" customWidth="1"/>
@@ -385,7 +394,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -569,7 +578,7 @@
         <v>46111</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -613,10 +622,10 @@
         <v>46113</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C23">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -624,10 +633,43 @@
         <v>46125</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C24">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vani1\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E44A20C-6020-4C2A-8C94-FEE4791FC16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB848757-9DFC-4686-B5EA-93B7FFDB71E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Date</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>scraped more baumkataster datasets for Innsbruck and Linz</t>
+  </si>
+  <si>
+    <t>scraped additional viennese context data</t>
   </si>
 </sst>
 </file>
@@ -360,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.1796875" customWidth="1"/>
@@ -394,7 +397,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -669,6 +672,17 @@
         <v>26</v>
       </c>
       <c r="C27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28">
         <v>6</v>
       </c>
     </row>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vani1\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB848757-9DFC-4686-B5EA-93B7FFDB71E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897CF734-29C3-4869-B769-BFCE9710992E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -129,6 +129,12 @@
   </si>
   <si>
     <t>scraped additional viennese context data</t>
+  </si>
+  <si>
+    <t>adjusted BEAM, finalized code, started new notebook to document scraping new data</t>
+  </si>
+  <si>
+    <t>scraped sentinel-2 data for 5 cities (3 seasons again), adjusted BEAM again, wrote chapters for Draft Report &amp; Slides</t>
   </si>
 </sst>
 </file>
@@ -363,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.1796875" customWidth="1"/>
@@ -397,7 +403,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -683,6 +689,28 @@
         <v>30</v>
       </c>
       <c r="C28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30">
         <v>6</v>
       </c>
     </row>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vani1\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897CF734-29C3-4869-B769-BFCE9710992E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600F84E2-ADBB-4EAF-AA4D-73E65E933568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Date</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>scraped sentinel-2 data for 5 cities (3 seasons again), adjusted BEAM again, wrote chapters for Draft Report &amp; Slides</t>
+  </si>
+  <si>
+    <t>finished my chapters and fixed Draft BEAM</t>
   </si>
 </sst>
 </file>
@@ -369,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.1796875" customWidth="1"/>
@@ -403,7 +406,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -712,6 +715,17 @@
       </c>
       <c r="C30">
         <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
+        <v>46172</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vani1\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600F84E2-ADBB-4EAF-AA4D-73E65E933568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB16CC1-D83D-46B6-B4A5-26A98C92999D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -137,7 +137,7 @@
     <t>scraped sentinel-2 data for 5 cities (3 seasons again), adjusted BEAM again, wrote chapters for Draft Report &amp; Slides</t>
   </si>
   <si>
-    <t>finished my chapters and fixed Draft BEAM</t>
+    <t>finished my chapters and fixed Draft BEAM and finished Draft Slides</t>
   </si>
 </sst>
 </file>
@@ -406,7 +406,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -725,7 +725,7 @@
         <v>33</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/timesheets/Nina.xlsx
+++ b/timesheets/Nina.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vani1\Desktop\wu_dslab_infrared-city\timesheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB16CC1-D83D-46B6-B4A5-26A98C92999D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D196C1-7F18-4726-9DCE-589FDD839896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Date</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>finished my chapters and fixed Draft BEAM and finished Draft Slides</t>
+  </si>
+  <si>
+    <t>adjusting slides</t>
   </si>
 </sst>
 </file>
@@ -372,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.1796875" customWidth="1"/>
@@ -406,7 +409,7 @@
       </c>
       <c r="H2">
         <f>SUM(C:C)</f>
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -726,6 +729,17 @@
       </c>
       <c r="C31">
         <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
